--- a/premise/data/additional_inventories/lci-batteries-vanadium.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-vanadium.xlsx
@@ -9593,7 +9593,9 @@
       </ns0:c>
       <ns0:c r="B280" t="inlineStr">
         <ns0:is>
-          <ns0:t>Source: Weber et al. (2018). Life cycle assessment of a vanadium redox flow battery. Environmental science &amp; technology, 52(18), 10864-10873. https://doi.org/10.1021/acs.est.8b02073</ns0:t>
+          <ns0:t>APPROVED SBR PROCESS-WATER VOLUME REFERENCE, issue102, 2026-10-18. Crenna2021 DOI10.1016/j.resconrec.2021.105619 documentsSBRasbatterybinder;recoveredSI doesnotverifythemanufacturing-waterrecipe. TheexistingpremiseSBRprovidercontains1.8kgdeionizedprocesswater/kgdrySBRand0.25m3coolingwaterresource;threecopieshave1.8m3unpollutedWWT. Sourcewater-to-wastewatertreatmentbasiswasnotindependentlyrecovered;thisisexplicitphysicalreferencecorrection,notclaimedverifiedsourceerratum. Existing1.8m3processWWTis1800kgliquidandcannotfollowfrom1.8kgprocesswater plus250kgcoolingwaterwithoutunreported&gt;1548kgwaterfeed. Modelall1.8kgdeionizedprocesswaterassenttoprocessWWT:1.8/1000=0.0018m3at1000kg/m3. Thisassignmentisexplicitengineeringwaterfate;sourceoriginalWWTunitnotverified,notclaimthatallindustrialsewerisexactly1.8L. Keep0.25m3coolingwithdrawal,separatefromprocesswater;coolingreturncompartment/temperatureandconsumptivefractionremainunresolvedandarenotinvented.0-100%coolingreturn sensitivityrequired;noextra0.25m3WWTassumed. Existingheat/emissionquantitiesretained,notinventfullthermalbalance. Polymermonomers,output1kgdrySBR,energyandallmetalcoefficients unchanged. Samecorrectioninall3copiespreventsdefaultversion/importorderfromrestoringwrongvolume. DoesnotvalidateSBRwastewaterpollutantloadorwholeindustrialwaterbalance.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Weber et al. (2018). Life cycle assessment of a vanadium redox flow battery. Environmental science &amp; technology, 52(18), 10864-10873. https://doi.org/10.1021/acs.est.8b02073</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -9710,6 +9712,11 @@
           <ns0:t>reference product</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="H288" t="inlineStr">
+        <ns0:is>
+          <ns0:t>comment</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="289">
       <ns0:c r="A289" t="inlineStr">
@@ -9735,6 +9742,11 @@
           <ns0:t>biosphere</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="H289" t="inlineStr">
+        <ns0:is>
+          <ns0:t>APPROVED SBR PROCESS-WATER VOLUME REFERENCE, issue102, 2026-10-18. Crenna2021 DOI10.1016/j.resconrec.2021.105619 documentsSBRasbatterybinder;recoveredSI doesnotverifythemanufacturing-waterrecipe. TheexistingpremiseSBRprovidercontains1.8kgdeionizedprocesswater/kgdrySBRand0.25m3coolingwaterresource;threecopieshave1.8m3unpollutedWWT. Sourcewater-to-wastewatertreatmentbasiswasnotindependentlyrecovered;thisisexplicitphysicalreferencecorrection,notclaimedverifiedsourceerratum. Existing1.8m3processWWTis1800kgliquidandcannotfollowfrom1.8kgprocesswater plus250kgcoolingwaterwithoutunreported&gt;1548kgwaterfeed. Modelall1.8kgdeionizedprocesswaterassenttoprocessWWT:1.8/1000=0.0018m3at1000kg/m3. Thisassignmentisexplicitengineeringwaterfate;sourceoriginalWWTunitnotverified,notclaimthatallindustrialsewerisexactly1.8L. Keep0.25m3coolingwithdrawal,separatefromprocesswater;coolingreturncompartment/temperatureandconsumptivefractionremainunresolvedandarenotinvented.0-100%coolingreturn sensitivityrequired;noextra0.25m3WWTassumed. Existingheat/emissionquantitiesretained,notinventfullthermalbalance. Polymermonomers,output1kgdrySBR,energyandallmetalcoefficients unchanged. Samecorrectioninall3copiespreventsdefaultversion/importorderfromrestoringwrongvolume. DoesnotvalidateSBRwastewaterpollutantloadorwholeindustrialwaterbalance.</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="290">
       <ns0:c r="A290" t="inlineStr">
@@ -10063,7 +10075,7 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="B301" t="n">
-        <ns0:v>-1.8</ns0:v>
+        <ns0:v>-0.0018</ns0:v>
       </ns0:c>
       <ns0:c r="C301" t="inlineStr">
         <ns0:is>
@@ -10083,6 +10095,11 @@
       <ns0:c r="G301" t="inlineStr">
         <ns0:is>
           <ns0:t>wastewater, unpolluted</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H301" t="inlineStr">
+        <ns0:is>
+          <ns0:t>APPROVED SBR PROCESS-WATER VOLUME REFERENCE, issue102, 2026-10-18. Crenna2021 DOI10.1016/j.resconrec.2021.105619 documentsSBRasbatterybinder;recoveredSI doesnotverifythemanufacturing-waterrecipe. TheexistingpremiseSBRprovidercontains1.8kgdeionizedprocesswater/kgdrySBRand0.25m3coolingwaterresource;threecopieshave1.8m3unpollutedWWT. Sourcewater-to-wastewatertreatmentbasiswasnotindependentlyrecovered;thisisexplicitphysicalreferencecorrection,notclaimedverifiedsourceerratum. Existing1.8m3processWWTis1800kgliquidandcannotfollowfrom1.8kgprocesswater plus250kgcoolingwaterwithoutunreported&gt;1548kgwaterfeed. Modelall1.8kgdeionizedprocesswaterassenttoprocessWWT:1.8/1000=0.0018m3at1000kg/m3. Thisassignmentisexplicitengineeringwaterfate;sourceoriginalWWTunitnotverified,notclaimthatallindustrialsewerisexactly1.8L. Keep0.25m3coolingwithdrawal,separatefromprocesswater;coolingreturncompartment/temperatureandconsumptivefractionremainunresolvedandarenotinvented.0-100%coolingreturn sensitivityrequired;noextra0.25m3WWTassumed. Existingheat/emissionquantitiesretained,notinventfullthermalbalance. Polymermonomers,output1kgdrySBR,energyandallmetalcoefficients unchanged. Samecorrectioninall3copiespreventsdefaultversion/importorderfromrestoringwrongvolume. DoesnotvalidateSBRwastewaterpollutantloadorwholeindustrialwaterbalance.</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
